--- a/Result/profitability/4306.xlsx
+++ b/Result/profitability/4306.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.73</v>
       </c>
       <c r="M2" t="n">
-        <v>0.185</v>
+        <v>0.21875</v>
       </c>
       <c r="N2" t="n">
-        <v>15.4025</v>
+        <v>15.65</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.78</v>
       </c>
       <c r="M3" t="n">
-        <v>0.25</v>
+        <v>0.3175</v>
       </c>
       <c r="N3" t="n">
-        <v>15.34125</v>
+        <v>15.925</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>1.47</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4349999999999999</v>
+        <v>0.48625</v>
       </c>
       <c r="N4" t="n">
-        <v>15.485</v>
+        <v>15.6525</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.37</v>
       </c>
       <c r="M5" t="n">
-        <v>0.46625</v>
+        <v>0.5337500000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>14.52125</v>
+        <v>14.915</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1042,7 +1042,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
         <v>97.40000000000001</v>
@@ -1137,13 +1137,13 @@
         <v>0.49</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5287499999999999</v>
+        <v>0.5774999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>14.84</v>
+        <v>15.2925</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
@@ -1152,10 +1152,10 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>1.26</v>
       </c>
       <c r="M7" t="n">
-        <v>0.66875</v>
+        <v>0.7337499999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>15.45</v>
+        <v>15.82625</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.74</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7599999999999999</v>
+        <v>0.7962499999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>15.5925</v>
+        <v>15.7275</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>4306</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>3960</v>
+      </c>
+      <c r="D75" t="n">
+        <v>3242</v>
+      </c>
+      <c r="E75" t="n">
+        <v>718</v>
+      </c>
+      <c r="F75" t="n">
+        <v>18.12</v>
+      </c>
+      <c r="G75" t="n">
+        <v>280</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>7.06%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>161</v>
+      </c>
+      <c r="J75" t="n">
+        <v>440</v>
+      </c>
+      <c r="K75" t="n">
+        <v>349</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="N75" t="n">
+        <v>15.76375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.208333333333333</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>1.080000000000002</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.06338028169014098</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-54</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.2104208416833668</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
